--- a/uploaded_resumes.xlsx
+++ b/uploaded_resumes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,414 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>**John Doe**  
+1234 Elm Street, City, State, ZIP  
+(123) 456-7890 | johndoe@email.com | linkedin.com/in/johndoe | github.com/johndoe  
+---
+### **Professional Summary**  
+Highly skilled Software Engineer with **X** years of experience in designing, developing, and maintaining software applications. Expertise in **full-stack development, cloud computing, and DevOps**. Adept at problem-solving and optimizing software for efficiency and scalability.
+---
+### **Core Competencies**  
+- **Software Development:** Designing, developing, and maintaining robust applications.
+- **Programming Languages:** Python, Java, JavaScript, C++.
+- **Web Development:** React.js, Node.js, Django, Flask.
+- **Database Management:** MySQL, PostgreSQL, MongoDB.
+- **Cloud &amp; DevOps:** AWS, Docker, Kubernetes, CI/CD pipelines.
+- **Testing &amp; Debugging:** JUnit, Selenium, Postman.
+---
+### **Professional Experience**  
+**Software Engineer**  
+ABC Tech Solutions | City, State | *MM/YYYY – Present*  
+- Developed and maintained scalable software applications, ensuring high performance and reliability.
+- Optimized system architecture, reducing downtime and increasing efficiency.
+- Implemented RESTful APIs and integrated third-party services to enhance application functionality.
+- Collaborated with cross-functional teams to define project requirements and deliver solutions.
+**Software Developer**  
+XYZ Innovations | City, State | *MM/YYYY – MM/YYYY*  
+- Designed and built interactive web applications to enhance user experience.
+- Conducted thorough testing and debugging to ensure software quality.
+- Managed software updates and feature enhancements to improve performance.
+---
+### **Education**  
+**Bachelor of Science in Computer Science**  
+University of XYZ, City, State  
+*Graduation Year: YYYY*  
+---
+### **Certifications**  
+- AWS Certified Solutions Architect  
+- Google Associate Cloud Engineer  
+- Full-Stack Web Development Certification (Coursera/Udemy)  
+---
+### **Key Projects**  
+**Enterprise Software Solution**  
+- Developed and maintained a cloud-based enterprise software system for streamlined operations.
+- Improved system efficiency by implementing optimized database queries and caching strategies.
+**E-commerce Platform**  
+- Built a full-stack e-commerce application with secure authentication and real-time payment processing.
+- Integrated a scalable architecture for handling high user traffic.
+---
+### **Soft Skills**  
+- Problem-Solving &amp; Critical Thinking  
+- Effective Communication  
+- Team Collaboration  
+- Adaptability &amp; Continuous Learning  
+---
+### **Languages**  
+- English (Fluent)  
+- Spanish (Intermediate)  
+---
+Available upon request: **References**</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
